--- a/flare-pwr/SMR_Case/CaseLBLOCA_cold_in.xlsx
+++ b/flare-pwr/SMR_Case/CaseLBLOCA_cold_in.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/flare-pwr/Examples/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/26b11560d98c47b3/Documents/Current Work Activities/FLASH Model/Integrated Model/flare-pwr/SMR_Case/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="11_6347EE8A944C94BE6D09D0D64E5DCE3AD7408283" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97634FDE-AEB6-4188-80E9-D4CE85BF2A40}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="11_6347EE8A944C94BE6D09D0D64E5DCE3AD7408283" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54C3FEAD-27AB-4454-A378-A54D23AE9BA1}"/>
   <bookViews>
-    <workbookView xWindow="525" yWindow="1440" windowWidth="15840" windowHeight="9150" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="-11220" windowWidth="16665" windowHeight="9765" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CaseLBLOCA_cold_in" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="259">
   <si>
     <t># CaseLBLOCA_cold_in
 # Cold-leg double-ended guillotine break (0.20 m). Full core model + DNBR.
@@ -346,42 +346,6 @@
     <t>Very low water level, all cooling is lost</t>
   </si>
   <si>
-    <t xml:space="preserve">   source_term_model = "RG1183_LOCA"</t>
-  </si>
-  <si>
-    <t>nbt_leak_rate_frac_per_day = 0.005    # containment leak rate [frac/day]</t>
-  </si>
-  <si>
-    <t>nbt_sprays_on = False    # containment sprays not credited</t>
-  </si>
-  <si>
-    <t>nbt_wind_speed_m_s = 0.33    # wind speed [m/s]</t>
-  </si>
-  <si>
-    <t>nbt_distance_eab_m = 805.0    # EAB distance [m]</t>
-  </si>
-  <si>
-    <t>nbt_distance_lpz_m = 1610.0    # LPZ distance [m]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   nbt_eab_integration_hr = 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   nbt_lpz_integration_hr = 8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   nbt_gap_release_duration_hr = 0.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   nbt_early_iv_duration_hr = 1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   nbt_credit_decay = False</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   nbt_credit_deposition = False</t>
-  </si>
-  <si>
     <t>Hold value</t>
   </si>
   <si>
@@ -776,6 +740,66 @@
   </si>
   <si>
     <t>endtime = 1200    # captures depressurisation, uncovery, and reflood [s]</t>
+  </si>
+  <si>
+    <t>nbt_containment_volume_ft3 = 450000.0</t>
+  </si>
+  <si>
+    <t>nbt_leak_rate_frac_per_day = 0.002    # 0.2%/day typical PWR TS limit</t>
+  </si>
+  <si>
+    <t>nbt_sprays_on = False</t>
+  </si>
+  <si>
+    <t>nbt_wind_speed_m_s = .33    # Conservative value</t>
+  </si>
+  <si>
+    <t>nbt_stability_class = "F"    # F = most conservative for EAB dose</t>
+  </si>
+  <si>
+    <t>nbt_release_height_m = 0.0    # Ground level</t>
+  </si>
+  <si>
+    <t>nbt_distance_eab_m = 335.0    #</t>
+  </si>
+  <si>
+    <t>nbt_distance_lpz_m = 1610.0    # ~3 miles</t>
+  </si>
+  <si>
+    <t>nbt_distance_cr_intake_m = 100.0</t>
+  </si>
+  <si>
+    <t>nbt_cr_flow_cfm = 100.0</t>
+  </si>
+  <si>
+    <t>nbt_cr_volume_ft3 = 10000.0</t>
+  </si>
+  <si>
+    <t>nbt_cr_filter_on = True</t>
+  </si>
+  <si>
+    <t>nbt_eab_integration_hr = 2.0</t>
+  </si>
+  <si>
+    <t>nbt_lpz_integration_hr = 8.0    # nbt_end_time_hr = 30*24.0    # dose integration end time [hr]</t>
+  </si>
+  <si>
+    <t>nbt_breathing_rate_m3_s = 0.000347    # NRC standard value</t>
+  </si>
+  <si>
+    <t>nbt_burnup_gwdmtu = 51    # 51 GWd/MTU e.g., CRN ESPA (SSAR Sec. 15.2, ML19030A354)</t>
+  </si>
+  <si>
+    <t>nbt_gap_release_duration_hr = 0.5</t>
+  </si>
+  <si>
+    <t>nbt_early_iv_duration_hr = 1.3</t>
+  </si>
+  <si>
+    <t>nbt_credit_decay = False    # RG 1.183 LBLOCA default</t>
+  </si>
+  <si>
+    <t>nbt_credit_deposition = False    # RG 1.183 LBLOCA default</t>
   </si>
 </sst>
 </file>
@@ -893,7 +917,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -911,7 +935,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
@@ -1286,7 +1309,7 @@
     </row>
     <row r="5" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B5" s="3"/>
     </row>
@@ -1484,7 +1507,7 @@
     </row>
     <row r="38" spans="1:2" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="4" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B38" s="4"/>
     </row>
@@ -1663,7 +1686,7 @@
     </row>
     <row r="68" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A68" s="4" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>106</v>
@@ -1710,8 +1733,8 @@
       <c r="B75" s="4"/>
     </row>
     <row r="76" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
-      <c r="A76" t="s">
-        <v>107</v>
+      <c r="A76" s="4" t="s">
+        <v>239</v>
       </c>
       <c r="B76" s="4"/>
       <c r="F76" s="4" t="s">
@@ -1721,7 +1744,7 @@
     </row>
     <row r="77" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A77" s="4" t="s">
-        <v>70</v>
+        <v>240</v>
       </c>
       <c r="B77" s="4"/>
       <c r="F77" s="4" t="s">
@@ -1733,7 +1756,7 @@
     </row>
     <row r="78" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A78" s="4" t="s">
-        <v>108</v>
+        <v>241</v>
       </c>
       <c r="B78" s="4"/>
       <c r="F78" s="4" t="s">
@@ -1743,7 +1766,7 @@
     </row>
     <row r="79" spans="1:7" s="1" customFormat="1" ht="15.95" customHeight="1">
       <c r="A79" s="4" t="s">
-        <v>109</v>
+        <v>242</v>
       </c>
       <c r="B79" s="4"/>
       <c r="F79" s="4" t="s">
@@ -1755,7 +1778,7 @@
     </row>
     <row r="80" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A80" s="4" t="s">
-        <v>110</v>
+        <v>243</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>76</v>
@@ -1764,7 +1787,7 @@
     </row>
     <row r="81" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A81" s="4" t="s">
-        <v>79</v>
+        <v>244</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>77</v>
@@ -1775,7 +1798,7 @@
     </row>
     <row r="82" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A82" s="4" t="s">
-        <v>81</v>
+        <v>245</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>79</v>
@@ -1786,7 +1809,7 @@
     </row>
     <row r="83" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A83" s="4" t="s">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>81</v>
@@ -1797,7 +1820,7 @@
     </row>
     <row r="84" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A84" s="4" t="s">
-        <v>112</v>
+        <v>247</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>83</v>
@@ -1808,7 +1831,7 @@
     </row>
     <row r="85" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A85" s="4" t="s">
-        <v>87</v>
+        <v>248</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>85</v>
@@ -1819,7 +1842,7 @@
     </row>
     <row r="86" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A86" s="4" t="s">
-        <v>88</v>
+        <v>249</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>87</v>
@@ -1828,7 +1851,7 @@
     </row>
     <row r="87" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A87" s="4" t="s">
-        <v>89</v>
+        <v>250</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>88</v>
@@ -1837,7 +1860,7 @@
     </row>
     <row r="88" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A88" s="4" t="s">
-        <v>90</v>
+        <v>251</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>89</v>
@@ -1845,8 +1868,8 @@
       <c r="G88" s="4"/>
     </row>
     <row r="89" spans="1:7" s="1" customFormat="1" ht="16.5" customHeight="1">
-      <c r="A89" s="7" t="s">
-        <v>113</v>
+      <c r="A89" s="4" t="s">
+        <v>252</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>90</v>
@@ -1854,8 +1877,8 @@
       <c r="G89" s="4"/>
     </row>
     <row r="90" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A90" s="7" t="s">
-        <v>114</v>
+      <c r="A90" s="4" t="s">
+        <v>253</v>
       </c>
       <c r="F90" s="4" t="s">
         <v>91</v>
@@ -1864,7 +1887,7 @@
     </row>
     <row r="91" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
       <c r="A91" s="4" t="s">
-        <v>92</v>
+        <v>254</v>
       </c>
       <c r="F91" s="4" t="s">
         <v>92</v>
@@ -1874,8 +1897,8 @@
       </c>
     </row>
     <row r="92" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A92" t="s">
-        <v>115</v>
+      <c r="A92" s="4" t="s">
+        <v>255</v>
       </c>
       <c r="F92" s="4" t="s">
         <v>94</v>
@@ -1885,18 +1908,18 @@
       </c>
     </row>
     <row r="93" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A93" t="s">
-        <v>116</v>
+      <c r="A93" s="4" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="94" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A94" t="s">
-        <v>117</v>
+      <c r="A94" s="4" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="95" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1">
-      <c r="A95" t="s">
-        <v>118</v>
+      <c r="A95" s="4" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:7" s="1" customFormat="1" ht="15" customHeight="1"/>
@@ -6064,837 +6087,837 @@
   <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="48" style="8" customWidth="1"/>
-    <col min="2" max="2" width="20.5703125" style="8" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" style="8" customWidth="1"/>
-    <col min="4" max="4" width="59.42578125" style="8" customWidth="1"/>
-    <col min="5" max="6" width="13.7109375" style="8" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="8"/>
+    <col min="1" max="1" width="48" style="7" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" style="7" customWidth="1"/>
+    <col min="4" max="4" width="59.42578125" style="7" customWidth="1"/>
+    <col min="5" max="6" width="13.7109375" style="7" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="36">
-      <c r="A1" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
+      <c r="A1" s="14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
+      <c r="A2" s="13" t="s">
+        <v>234</v>
+      </c>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="4" spans="1:6" ht="15">
-      <c r="A4" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="B5" s="7">
+        <v>10000</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="B6" s="7">
+        <v>435.62599999999998</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="B7" s="7">
+        <v>2585.3270000000002</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="7">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="B9" s="7">
+        <v>19</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="B10" s="7">
+        <v>50</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7" t="s">
+        <v>218</v>
+      </c>
+      <c r="B11" s="7">
+        <v>7800</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="B12" s="7">
+        <v>500</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="B13" s="7">
+        <v>1E-3</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="B14" s="7">
+        <v>2.5999999999999999E-2</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="B16" s="7">
+        <v>2300</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="B17" s="7">
+        <v>900</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="7" t="s">
+        <v>201</v>
+      </c>
+      <c r="B18" s="7">
+        <v>1.5</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="B19" s="7">
+        <v>517</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="B20" s="7">
+        <v>177</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="A22" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="B22" s="7">
+        <v>1</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="B23" s="7">
+        <v>0</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="A24" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="B24" s="7">
+        <v>15</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15">
+      <c r="A26" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="A27" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="7">
+        <v>101.325</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15">
+      <c r="A28" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B28" s="9">
+        <v>27</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B29" s="7">
+        <v>27</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15">
+      <c r="A30" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="B30" s="9">
+        <v>0.2</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+    </row>
+    <row r="32" spans="1:6" ht="15">
+      <c r="A32" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+    </row>
+    <row r="33" spans="1:6" ht="15">
+      <c r="A33" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B33" s="8">
+        <v>86400</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="E33" s="8"/>
+      <c r="F33" s="8"/>
+    </row>
+    <row r="34" spans="1:6" ht="15">
+      <c r="A34" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="B34" s="8">
+        <v>2</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E34" s="8"/>
+      <c r="F34" s="8"/>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" s="7">
+        <v>1</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="B39" s="7">
+        <v>575</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D39" s="7" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B41" s="7">
+        <v>2738</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="B42" s="7">
+        <v>300</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="15">
+      <c r="A44" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C44" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B45" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="B47" s="7">
+        <v>0.8</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" s="7">
+        <v>0</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
+      <c r="A49" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="B49" s="7">
+        <v>0</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B50" s="7">
+        <v>0</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="7">
+        <v>0</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" s="7">
+        <v>27</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D52" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="8" t="s">
-        <v>244</v>
-      </c>
-      <c r="B5" s="8">
-        <v>10000</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>243</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="8" t="s">
-        <v>241</v>
-      </c>
-      <c r="B6" s="8">
-        <v>435.62599999999998</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="B7" s="8">
-        <v>2585.3270000000002</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="B8" s="8">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" s="8">
-        <v>19</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="B10" s="8">
-        <v>50</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="B11" s="8">
-        <v>7800</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="B12" s="8">
+    </row>
+    <row r="54" spans="1:6" ht="15">
+      <c r="A54" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B54" s="9">
         <v>500</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="B13" s="8">
-        <v>1E-3</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="8">
-        <v>2.5999999999999999E-2</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="B16" s="8">
-        <v>2300</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="B17" s="8">
-        <v>900</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="8" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="B19" s="8">
-        <v>517</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B20" s="8">
-        <v>177</v>
-      </c>
-      <c r="C20" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>205</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="B22" s="8">
-        <v>1</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="B23" s="8">
-        <v>0</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="B24" s="8">
-        <v>15</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15">
-      <c r="A26" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="B27" s="8">
-        <v>101.325</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15">
-      <c r="A28" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="B28" s="10">
+      <c r="C54" s="9" t="s">
+        <v>121</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+    </row>
+    <row r="55" spans="1:6" ht="15">
+      <c r="A55" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+    </row>
+    <row r="56" spans="1:6">
+      <c r="A56" s="7">
+        <v>0</v>
+      </c>
+      <c r="B56" s="7">
+        <v>0</v>
+      </c>
+      <c r="C56" s="7">
         <v>27</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="10" t="s">
-        <v>192</v>
-      </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B29" s="8">
+      <c r="D56" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
+      <c r="A57" s="7">
+        <v>86400</v>
+      </c>
+      <c r="B57" s="7">
+        <v>0</v>
+      </c>
+      <c r="C57" s="7">
         <v>27</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15">
-      <c r="A30" s="10" t="s">
-        <v>189</v>
-      </c>
-      <c r="B30" s="10">
-        <v>0.2</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>188</v>
-      </c>
-      <c r="E30" s="10"/>
-      <c r="F30" s="10"/>
-    </row>
-    <row r="32" spans="1:6" ht="15">
-      <c r="A32" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-    </row>
-    <row r="33" spans="1:6" ht="15">
-      <c r="A33" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="B33" s="9">
+      <c r="D57" s="7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="15">
+      <c r="A59" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+    </row>
+    <row r="60" spans="1:6" ht="15">
+      <c r="A60" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" s="8"/>
+      <c r="F60" s="8"/>
+    </row>
+    <row r="61" spans="1:6">
+      <c r="A61" s="7">
+        <v>0</v>
+      </c>
+      <c r="B61" s="7">
+        <v>0</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
+      <c r="A62" s="7">
+        <v>5400</v>
+      </c>
+      <c r="B62" s="7">
+        <v>0</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
+      <c r="A63" s="7">
+        <v>5401</v>
+      </c>
+      <c r="B63" s="7">
+        <v>5</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
+      <c r="A64" s="7">
         <v>86400</v>
       </c>
-      <c r="C33" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="1:6" ht="15">
-      <c r="A34" s="9" t="s">
-        <v>184</v>
-      </c>
-      <c r="B34" s="9">
-        <v>2</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="8" t="s">
-        <v>182</v>
-      </c>
-      <c r="B35" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="8" t="s">
-        <v>179</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="B37" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="8" t="s">
-        <v>172</v>
-      </c>
-      <c r="B38" s="8">
-        <v>1</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="B39" s="8">
-        <v>575</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="8" t="s">
-        <v>167</v>
-      </c>
-      <c r="B40" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="B41" s="8">
-        <v>2738</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>163</v>
-      </c>
-      <c r="D41" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B42" s="8">
-        <v>300</v>
-      </c>
-      <c r="C42" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="15">
-      <c r="A44" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="B44" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>157</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>123</v>
-      </c>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="8" t="s">
-        <v>156</v>
-      </c>
-      <c r="B45" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B46" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="C46" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47" s="8" t="s">
-        <v>151</v>
-      </c>
-      <c r="B47" s="8">
-        <v>0.8</v>
-      </c>
-      <c r="C47" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48" s="8" t="s">
-        <v>148</v>
-      </c>
-      <c r="B48" s="8">
-        <v>0</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>147</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="8">
-        <v>0</v>
-      </c>
-      <c r="C49" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="8" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="B50" s="8">
-        <v>0</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B51" s="8">
-        <v>0</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="D51" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="B52" s="8">
-        <v>27</v>
-      </c>
-      <c r="C52" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="15">
-      <c r="A54" s="10" t="s">
-        <v>134</v>
-      </c>
-      <c r="B54" s="10">
-        <v>500</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>133</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>132</v>
-      </c>
-      <c r="E54" s="10"/>
-      <c r="F54" s="10"/>
-    </row>
-    <row r="55" spans="1:6" ht="15">
-      <c r="A55" s="9" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>130</v>
-      </c>
-      <c r="C55" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D55" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="9"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56" s="8">
-        <v>0</v>
-      </c>
-      <c r="B56" s="8">
-        <v>0</v>
-      </c>
-      <c r="C56" s="8">
-        <v>27</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57" s="8">
-        <v>86400</v>
-      </c>
-      <c r="B57" s="8">
-        <v>0</v>
-      </c>
-      <c r="C57" s="8">
-        <v>27</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="15">
-      <c r="A59" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="B59" s="10"/>
-      <c r="C59" s="10"/>
-      <c r="D59" s="10"/>
-      <c r="E59" s="10"/>
-      <c r="F59" s="10"/>
-    </row>
-    <row r="60" spans="1:6" ht="15">
-      <c r="A60" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="B60" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C60" s="9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D60" s="9"/>
-      <c r="E60" s="9"/>
-      <c r="F60" s="9"/>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61" s="8">
-        <v>0</v>
-      </c>
-      <c r="B61" s="8">
-        <v>0</v>
-      </c>
-      <c r="C61" s="8" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="8">
-        <v>5400</v>
-      </c>
-      <c r="B62" s="8">
-        <v>0</v>
-      </c>
-      <c r="C62" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63" s="8">
-        <v>5401</v>
-      </c>
-      <c r="B63" s="8">
+      <c r="B64" s="7">
         <v>5</v>
       </c>
-      <c r="C63" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64" s="8">
-        <v>86400</v>
-      </c>
-      <c r="B64" s="8">
-        <v>5</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>119</v>
+      <c r="C64" s="7" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="15">
-      <c r="A66" s="10"/>
-      <c r="B66" s="10"/>
-      <c r="C66" s="10"/>
-      <c r="D66" s="10"/>
-      <c r="E66" s="10"/>
-      <c r="F66" s="10"/>
+      <c r="A66" s="9"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
     </row>
     <row r="67" spans="1:6" ht="15">
-      <c r="A67" s="9"/>
-      <c r="B67" s="9"/>
-      <c r="C67" s="9"/>
-      <c r="D67" s="9"/>
-      <c r="E67" s="9"/>
-      <c r="F67" s="9"/>
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="8"/>
+      <c r="D67" s="8"/>
+      <c r="E67" s="8"/>
+      <c r="F67" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
